--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126545752</v>
       </c>
       <c r="B2" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126546308</v>
+        <v>126546026</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>58027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550572</v>
+        <v>550507</v>
       </c>
       <c r="R4" t="n">
-        <v>6411807</v>
+        <v>6411477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,32 +995,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126546026</v>
+        <v>126546308</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>57817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550507</v>
+        <v>550572</v>
       </c>
       <c r="R5" t="n">
-        <v>6411477</v>
+        <v>6411807</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1313,7 +1313,7 @@
         <v>126735004</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>126735004</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>126735004</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>126735004</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126735107</v>
       </c>
       <c r="B9" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>126546217</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>126546217</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>126735004</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126735107</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1313,7 +1313,7 @@
         <v>126735004</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>126735107</v>
       </c>
       <c r="B9" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>126546217</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32915-2025 artfynd.xlsx
+++ b/artfynd/A 32915-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>126546217</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
